--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753718880_h_5.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753718880_h_5.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.0259506897134711</v>
+        <v>0.01648986397775483</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008428503609948769</v>
+        <v>0.008414815340366153</v>
       </c>
       <c r="C2" t="n">
-        <v>31564890</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>31564890</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>21819396</v>
+        <v>4378149</v>
       </c>
       <c r="L2" t="n">
-        <v>11824034</v>
+        <v>2355432</v>
       </c>
       <c r="M2" t="n">
-        <v>2699013</v>
+        <v>533022</v>
       </c>
       <c r="N2" t="n">
-        <v>88471</v>
+        <v>16281</v>
       </c>
       <c r="O2" t="n">
-        <v>1622779</v>
+        <v>321162</v>
       </c>
       <c r="P2" t="n">
-        <v>638725</v>
+        <v>125469</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999944567680359</v>
+        <v>0.9999963641166687</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8542734384536743</v>
+        <v>0.8497234582901001</v>
       </c>
       <c r="S2" t="n">
-        <v>0.710486888885498</v>
+        <v>0.7052333354949951</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6334762573242188</v>
+        <v>0.623868465423584</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1794907748699188</v>
+        <v>0.1687325090169907</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6909964680671692</v>
+        <v>0.6835953593254089</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8010979294776917</v>
+        <v>0.8015190958976746</v>
       </c>
       <c r="X2" t="n">
-        <v>31564890</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>31564890</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>24075557</v>
+        <v>4837248</v>
       </c>
       <c r="AG2" t="n">
-        <v>14852679</v>
+        <v>2993650</v>
       </c>
       <c r="AH2" t="n">
-        <v>3997548</v>
+        <v>801659</v>
       </c>
       <c r="AI2" t="n">
-        <v>294942</v>
+        <v>59131</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2295467</v>
+        <v>459565</v>
       </c>
       <c r="AK2" t="n">
-        <v>900185</v>
+        <v>180092</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9565606117248535</v>
+        <v>0.9563066959381104</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112661480903625</v>
+        <v>0.9114376902580261</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580878376960754</v>
+        <v>0.8578296899795532</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6623296141624451</v>
+        <v>0.6616203784942627</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020044803619385</v>
+        <v>0.9018417000770569</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314298033714294</v>
+        <v>0.931449294090271</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.006352261232527649</v>
+        <v>0.003822833676019041</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002021233558325551</v>
+        <v>0.002016582438865534</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>21819396</v>
+        <v>4378149</v>
       </c>
       <c r="E3" t="n">
-        <v>3250785</v>
+        <v>661488</v>
       </c>
       <c r="F3" t="n">
-        <v>62794</v>
+        <v>10707</v>
       </c>
       <c r="G3" t="n">
-        <v>5378</v>
+        <v>934</v>
       </c>
       <c r="H3" t="n">
-        <v>3984</v>
+        <v>588</v>
       </c>
       <c r="I3" t="n">
-        <v>193</v>
+        <v>16</v>
       </c>
       <c r="J3" t="n">
-        <v>50082935</v>
+        <v>10069597</v>
       </c>
       <c r="K3" t="n">
-        <v>52783390</v>
+        <v>10589825</v>
       </c>
       <c r="L3" t="n">
-        <v>60508701</v>
+        <v>12141399</v>
       </c>
       <c r="M3" t="n">
-        <v>75425079</v>
+        <v>15159522</v>
       </c>
       <c r="N3" t="n">
-        <v>80797924</v>
+        <v>16246372</v>
       </c>
       <c r="O3" t="n">
-        <v>78376451</v>
+        <v>15757643</v>
       </c>
       <c r="P3" t="n">
-        <v>80522828</v>
+        <v>16191537</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.867827832698822</v>
+        <v>0.8666368722915649</v>
       </c>
       <c r="S3" t="n">
-        <v>0.724459707736969</v>
+        <v>0.7159150242805481</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5790262818336487</v>
+        <v>0.5700050592422485</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1985225975513458</v>
+        <v>0.1820753961801529</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6374173164367676</v>
+        <v>0.6300926208496094</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6608058214187622</v>
+        <v>0.6487773656845093</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>24075557</v>
+        <v>4837248</v>
       </c>
       <c r="Z3" t="n">
-        <v>989932</v>
+        <v>199108</v>
       </c>
       <c r="AA3" t="n">
-        <v>42706</v>
+        <v>8602</v>
       </c>
       <c r="AB3" t="n">
-        <v>33970</v>
+        <v>6851</v>
       </c>
       <c r="AC3" t="n">
-        <v>225</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>50083110</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>55412140</v>
+        <v>11143104</v>
       </c>
       <c r="AG3" t="n">
-        <v>63880556</v>
+        <v>12835014</v>
       </c>
       <c r="AH3" t="n">
-        <v>76325582</v>
+        <v>15348021</v>
       </c>
       <c r="AI3" t="n">
-        <v>81051985</v>
+        <v>16296339</v>
       </c>
       <c r="AJ3" t="n">
-        <v>78852750</v>
+        <v>15856274</v>
       </c>
       <c r="AK3" t="n">
-        <v>80615145</v>
+        <v>16209353</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575626254081726</v>
+        <v>0.957513689994812</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100250601768494</v>
+        <v>0.9098963737487793</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8576043844223022</v>
+        <v>0.8572810888290405</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6618287563323975</v>
+        <v>0.6612800359725952</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016448855400085</v>
+        <v>0.9016276001930237</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313045144081116</v>
+        <v>0.9312229752540588</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.06335324361862102</v>
+        <v>0.04802138549903948</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03189864197131144</v>
+        <v>0.03185715663591164</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>3503549</v>
+        <v>732624</v>
       </c>
       <c r="E4" t="n">
-        <v>11824034</v>
+        <v>2355432</v>
       </c>
       <c r="F4" t="n">
-        <v>874357</v>
+        <v>179495</v>
       </c>
       <c r="G4" t="n">
-        <v>39209</v>
+        <v>7698</v>
       </c>
       <c r="H4" t="n">
-        <v>73239</v>
+        <v>13737</v>
       </c>
       <c r="I4" t="n">
-        <v>6786</v>
+        <v>1114</v>
       </c>
       <c r="J4" t="n">
-        <v>175</v>
+        <v>23</v>
       </c>
       <c r="K4" t="n">
-        <v>3722070</v>
+        <v>774291</v>
       </c>
       <c r="L4" t="n">
-        <v>4818123</v>
+        <v>984501</v>
       </c>
       <c r="M4" t="n">
-        <v>1561625</v>
+        <v>321360</v>
       </c>
       <c r="N4" t="n">
-        <v>404429</v>
+        <v>80209</v>
       </c>
       <c r="O4" t="n">
-        <v>725683</v>
+        <v>148651</v>
       </c>
       <c r="P4" t="n">
-        <v>158587</v>
+        <v>31070</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999971985816956</v>
+        <v>0.999998152256012</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8609973192214966</v>
+        <v>0.8580968379974365</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7174053192138672</v>
+        <v>0.7105340957641602</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6050287485122681</v>
+        <v>0.5957217216491699</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1885275989770889</v>
+        <v>0.1751502156257629</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6631264090538025</v>
+        <v>0.6557544469833374</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7242202758789062</v>
+        <v>0.7171050310134888</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1020717</v>
+        <v>206350</v>
       </c>
       <c r="Z4" t="n">
-        <v>14852679</v>
+        <v>2993650</v>
       </c>
       <c r="AA4" t="n">
-        <v>414267</v>
+        <v>83345</v>
       </c>
       <c r="AB4" t="n">
-        <v>27445</v>
+        <v>5539</v>
       </c>
       <c r="AC4" t="n">
-        <v>5728</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>340</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1093320</v>
+        <v>221012</v>
       </c>
       <c r="AG4" t="n">
-        <v>1446268</v>
+        <v>290886</v>
       </c>
       <c r="AH4" t="n">
-        <v>661122</v>
+        <v>132861</v>
       </c>
       <c r="AI4" t="n">
-        <v>150368</v>
+        <v>30242</v>
       </c>
       <c r="AJ4" t="n">
-        <v>249384</v>
+        <v>50020</v>
       </c>
       <c r="AK4" t="n">
-        <v>66270</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9570613503456116</v>
+        <v>0.9569098353385925</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106451869010925</v>
+        <v>0.9106664061546326</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578459620475769</v>
+        <v>0.8575552701950073</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6620790362358093</v>
+        <v>0.661450207233429</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018246531486511</v>
+        <v>0.9017346501350403</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313670992851257</v>
+        <v>0.9313361048698425</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>147100</v>
+        <v>27342</v>
       </c>
       <c r="E5" t="n">
-        <v>1338220</v>
+        <v>278580</v>
       </c>
       <c r="F5" t="n">
-        <v>2699013</v>
+        <v>533022</v>
       </c>
       <c r="G5" t="n">
-        <v>131174</v>
+        <v>25477</v>
       </c>
       <c r="H5" t="n">
-        <v>315898</v>
+        <v>64901</v>
       </c>
       <c r="I5" t="n">
-        <v>29886</v>
+        <v>5795</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3323144</v>
+        <v>673735</v>
       </c>
       <c r="L5" t="n">
-        <v>4497142</v>
+        <v>934668</v>
       </c>
       <c r="M5" t="n">
-        <v>1962283</v>
+        <v>402096</v>
       </c>
       <c r="N5" t="n">
-        <v>357176</v>
+        <v>73138</v>
       </c>
       <c r="O5" t="n">
-        <v>923087</v>
+        <v>188544</v>
       </c>
       <c r="P5" t="n">
-        <v>327860</v>
+        <v>67924</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999978542327881</v>
+        <v>0.9999985694885254</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9137123227119446</v>
+        <v>0.9117918014526367</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8859094381332397</v>
+        <v>0.8830915689468384</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9568402171134949</v>
+        <v>0.9559298157691956</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9906721115112305</v>
+        <v>0.990658700466156</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9798063635826111</v>
+        <v>0.9794593453407288</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9940421581268311</v>
+        <v>0.9939696788787842</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>40062</v>
+        <v>8089</v>
       </c>
       <c r="Z5" t="n">
-        <v>425133</v>
+        <v>85507</v>
       </c>
       <c r="AA5" t="n">
-        <v>3997548</v>
+        <v>801659</v>
       </c>
       <c r="AB5" t="n">
-        <v>49729</v>
+        <v>9991</v>
       </c>
       <c r="AC5" t="n">
-        <v>145659</v>
+        <v>29239</v>
       </c>
       <c r="AD5" t="n">
-        <v>3165</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1066983</v>
+        <v>214636</v>
       </c>
       <c r="AG5" t="n">
-        <v>1468497</v>
+        <v>296450</v>
       </c>
       <c r="AH5" t="n">
-        <v>663748</v>
+        <v>133459</v>
       </c>
       <c r="AI5" t="n">
-        <v>150705</v>
+        <v>30288</v>
       </c>
       <c r="AJ5" t="n">
-        <v>250399</v>
+        <v>50141</v>
       </c>
       <c r="AK5" t="n">
-        <v>66400</v>
+        <v>13301</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.973541259765625</v>
+        <v>0.9734619855880737</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.964300811290741</v>
+        <v>0.964221715927124</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.983773410320282</v>
+        <v>0.9837768077850342</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963125586509705</v>
+        <v>0.9963127374649048</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938787817955017</v>
+        <v>0.9938985705375671</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983751177787781</v>
+        <v>0.9983823895454407</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>66923</v>
+        <v>13986</v>
       </c>
       <c r="E6" t="n">
-        <v>100844</v>
+        <v>19971</v>
       </c>
       <c r="F6" t="n">
-        <v>136625</v>
+        <v>28712</v>
       </c>
       <c r="G6" t="n">
-        <v>88471</v>
+        <v>16281</v>
       </c>
       <c r="H6" t="n">
-        <v>48115</v>
+        <v>9576</v>
       </c>
       <c r="I6" t="n">
-        <v>4641</v>
+        <v>886</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>32262</v>
+        <v>6517</v>
       </c>
       <c r="Z6" t="n">
-        <v>26748</v>
+        <v>5380</v>
       </c>
       <c r="AA6" t="n">
-        <v>54395</v>
+        <v>10917</v>
       </c>
       <c r="AB6" t="n">
-        <v>294942</v>
+        <v>59131</v>
       </c>
       <c r="AC6" t="n">
-        <v>34895</v>
+        <v>6993</v>
       </c>
       <c r="AD6" t="n">
-        <v>2405</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>4334</v>
+        <v>310</v>
       </c>
       <c r="E7" t="n">
-        <v>120410</v>
+        <v>23324</v>
       </c>
       <c r="F7" t="n">
-        <v>464235</v>
+        <v>97927</v>
       </c>
       <c r="G7" t="n">
-        <v>216975</v>
+        <v>43724</v>
       </c>
       <c r="H7" t="n">
-        <v>1622779</v>
+        <v>321162</v>
       </c>
       <c r="I7" t="n">
-        <v>117081</v>
+        <v>23259</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>139</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>4050</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>148103</v>
+        <v>29666</v>
       </c>
       <c r="AB7" t="n">
-        <v>37897</v>
+        <v>7595</v>
       </c>
       <c r="AC7" t="n">
-        <v>2295467</v>
+        <v>459565</v>
       </c>
       <c r="AD7" t="n">
-        <v>60210</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>78</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>164</v>
+        <v>29</v>
       </c>
       <c r="E8" t="n">
-        <v>7864</v>
+        <v>1138</v>
       </c>
       <c r="F8" t="n">
-        <v>23614</v>
+        <v>4519</v>
       </c>
       <c r="G8" t="n">
-        <v>11693</v>
+        <v>2376</v>
       </c>
       <c r="H8" t="n">
-        <v>284447</v>
+        <v>59849</v>
       </c>
       <c r="I8" t="n">
-        <v>638725</v>
+        <v>125469</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>140</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>405</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1651</v>
+        <v>331</v>
       </c>
       <c r="AB8" t="n">
-        <v>1327</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>62877</v>
+        <v>12595</v>
       </c>
       <c r="AD8" t="n">
-        <v>900185</v>
+        <v>180092</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
